--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/data/D1_recovery_event_audit.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/data/D1_recovery_event_audit.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S52"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,7 +541,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DO_1_2:step:20250923T10</t>
+          <t>DO_1_2:step:20251023T05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -550,32 +550,30 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>45923.41666666666</v>
+        <v>45953.20833333334</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>-0.4773090610576027</v>
+        <v>0.481475295095639</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>45925.625</v>
+        <v>45955.95833333334</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>direct_recovery</t>
+          <t>superseded</t>
         </is>
       </c>
       <c r="I2" t="b">
         <v>0</v>
       </c>
       <c r="J2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>53</v>
-      </c>
-      <c r="L2" t="n">
-        <v>53</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>0</v>
       </c>
@@ -588,15 +586,9 @@
       <c r="P2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="b">
-        <v>0</v>
-      </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2" t="b">
-        <v>0</v>
-      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -606,54 +598,66 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DO_1_2:step:20251020T04</t>
+          <t>DO_1_2:regime:pelt_20251024T22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>45950.16666666666</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>45955.95833333334</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>pelt_20251024T22</t>
+        </is>
+      </c>
       <c r="F3" t="n">
-        <v>0.08733778832289568</v>
+        <v>-0.5503466269381078</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>45955.95833333334</v>
+        <v>45960</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>superseded</t>
+          <t>adapted_recovery</t>
         </is>
       </c>
       <c r="I3" t="b">
         <v>0</v>
       </c>
       <c r="J3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>139</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+        <v>97</v>
+      </c>
+      <c r="L3" t="n">
+        <v>97</v>
+      </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>9</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>0</v>
+      </c>
+      <c r="R3" t="b">
+        <v>0</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -663,31 +667,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DO_1_2:regime:pelt_20251024T22</t>
+          <t>DO_1_2:step:20251117T10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>regime</t>
+          <t>step</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>45955.95833333334</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>pelt_20251024T22</t>
-        </is>
-      </c>
+        <v>45978.41666666666</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>-0.5477002137415199</v>
+        <v>-0.4494407109596825</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>45960</v>
+        <v>45980.625</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>adapted_recovery</t>
+          <t>direct_recovery</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -697,22 +697,22 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="L4" t="n">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
@@ -732,7 +732,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DO_1_2:step:20251117T00</t>
+          <t>DO_1_2:step:20251225T09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -741,14 +741,14 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>45978</v>
+        <v>46016.375</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>0.4728453445308849</v>
+        <v>-0.6807591322395412</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>45980.20833333334</v>
+        <v>46018.58333333334</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DO_1_2:step:20251201T10</t>
+          <t>DO_1_2:step:20260107T12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,14 +806,14 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>45992.41666666666</v>
+        <v>46029.5</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>0.3208388267951564</v>
+        <v>1.132361288765975</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>45994.625</v>
+        <v>46031.75</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -827,10 +827,10 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -857,12 +857,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DO_1_2</t>
+          <t>DO_1_3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DO_1_2:step:20251225T06</t>
+          <t>DO_1_3:step:20260411T10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -871,14 +871,14 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>46016.25</v>
+        <v>46123.41666666666</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>-0.1485541448983975</v>
+        <v>-0.003045321587230115</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46018.45833333334</v>
+        <v>46125.625</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -922,32 +922,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DO_1_2</t>
+          <t>DO_2_3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DO_1_2:step:20260107T09</t>
+          <t>DO_2_3:regime:20250914T06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>46029.375</v>
+        <v>45914.25</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>-0.6349075434251039</v>
+        <v>0.3553201329879724</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46032</v>
+        <v>45940.29166666666</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>direct_recovery</t>
+          <t>adapted_recovery</t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -957,22 +957,22 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>63</v>
+        <v>625</v>
       </c>
       <c r="L8" t="n">
-        <v>63</v>
+        <v>625</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q8" t="b">
         <v>0</v>
@@ -987,12 +987,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DO_1_2</t>
+          <t>DO_2_3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DO_1_2:step:20260218T03</t>
+          <t>DO_2_3:step:20260117T17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1001,14 +1001,14 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>46071.125</v>
+        <v>46039.70833333334</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>0.48358897718483</v>
+        <v>0.4734518386854905</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46073.33333333334</v>
+        <v>46041.91666666666</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1052,12 +1052,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DO_1_2</t>
+          <t>DO_2_3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DO_1_2:step:20260411T10</t>
+          <t>DO_2_3:step:20260323T15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1066,14 +1066,14 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>46123.41666666666</v>
+        <v>46104.625</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>0.1354714084634291</v>
+        <v>-0.1947254723789238</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46125.625</v>
+        <v>46106.83333333334</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1117,28 +1117,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DO_1_3</t>
+          <t>DO_2_3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DO_1_3:step:20250913T13</t>
+          <t>DO_2_3:regime:pelt_20260323T04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>45913.54166666666</v>
-      </c>
-      <c r="E11" t="inlineStr"/>
+        <v>46110</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>pelt_20260323T04</t>
+        </is>
+      </c>
       <c r="F11" t="n">
-        <v>-0.1037046057635246</v>
+        <v>-0.4847209874514191</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>45915.75</v>
+        <v>46111.70833333334</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1152,10 +1156,10 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="L11" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1182,12 +1186,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DO_1_3</t>
+          <t>DO_2_4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DO_1_3:step:20251022T23</t>
+          <t>DO_2_4:step:20251123T23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1196,14 +1200,14 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>45952.95833333334</v>
+        <v>45984.95833333334</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>0.3131945757979276</v>
+        <v>0.5426342871464527</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>45955.33333333334</v>
+        <v>45987.16666666666</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1217,10 +1221,10 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="L12" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1247,12 +1251,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DO_1_3</t>
+          <t>DO_2_4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DO_1_3:step:20251118T17</t>
+          <t>DO_2_4:step:20251223T11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1261,14 +1265,14 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>45979.70833333334</v>
+        <v>46014.45833333334</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>-0.5823165329295065</v>
+        <v>0.4394570935564274</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>45981.91666666666</v>
+        <v>46016.66666666666</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1312,32 +1316,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DO_1_3</t>
+          <t>ORP_1_2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DO_1_3:step:20260213T19</t>
+          <t>ORP_1_2:regime:20251227T00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>46066.79166666666</v>
+        <v>46018</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>0.1821498918914302</v>
+        <v>-138.3912907061892</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46069.45833333334</v>
+        <v>46029.33333333334</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>direct_recovery</t>
+          <t>adapted_recovery</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1347,22 +1351,22 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>64</v>
+        <v>272</v>
       </c>
       <c r="L14" t="n">
-        <v>64</v>
+        <v>272</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q14" t="b">
         <v>0</v>
@@ -1377,12 +1381,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DO_1_3</t>
+          <t>ORP_1_2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DO_1_3:step:20260411T07</t>
+          <t>ORP_1_2:step:20260116T00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1391,14 +1395,14 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>46123.29166666666</v>
+        <v>46038</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>-0.3029287184155237</v>
+        <v>-16.17389315344589</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46125.5</v>
+        <v>46040.20833333334</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1442,32 +1446,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DO_2_3</t>
+          <t>ORP_1_2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DO_2_3:step:20250806T22</t>
+          <t>ORP_1_2:regime:20260217T00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>45875.91666666666</v>
+        <v>46070</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>0.1770665825237464</v>
+        <v>101.0744659827315</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>45878.125</v>
+        <v>46090.29166666666</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>direct_recovery</t>
+          <t>adapted_recovery</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1477,22 +1481,22 @@
         <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>53</v>
+        <v>487</v>
       </c>
       <c r="L16" t="n">
-        <v>53</v>
+        <v>487</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q16" t="b">
         <v>0</v>
@@ -1507,12 +1511,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DO_2_3</t>
+          <t>ORP_1_3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DO_2_3:step:20250814T03</t>
+          <t>ORP_1_3:step:20250912T05</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1521,14 +1525,14 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>45883.125</v>
+        <v>45912.20833333334</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>-0.1978155355746012</v>
+        <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>45885.33333333334</v>
+        <v>45914.41666666666</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1572,12 +1576,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DO_2_3</t>
+          <t>ORP_1_3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DO_2_3:step:20250913T08</t>
+          <t>ORP_1_3:step:20251014T12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1586,14 +1590,14 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>45913.33333333334</v>
+        <v>45944.5</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>0.2002830962077073</v>
+        <v>-2.983812861087188</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>45924.25</v>
+        <v>45950.54166666666</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1607,13 +1611,13 @@
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>262</v>
+        <v>145</v>
       </c>
       <c r="L18" t="n">
-        <v>262</v>
+        <v>145</v>
       </c>
       <c r="M18" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N18" t="n">
         <v>2</v>
@@ -1637,12 +1641,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DO_2_3</t>
+          <t>ORP_1_3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DO_2_3:step:20251021T19</t>
+          <t>ORP_1_3:step:20251124T21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1651,14 +1655,14 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>45951.79166666666</v>
+        <v>45985.875</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>1.57302018728233</v>
+        <v>53.29738107292467</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>45954.70833333334</v>
+        <v>45988.08333333334</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1672,10 +1676,10 @@
         <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="L19" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -1702,12 +1706,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DO_2_3</t>
+          <t>ORP_1_3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DO_2_3:step:20251123T19</t>
+          <t>ORP_1_3:step:20251223T14</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1716,14 +1720,14 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>45984.79166666666</v>
+        <v>46014.58333333334</v>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>1.17453200921675</v>
+        <v>-35.6830734645392</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>45987.08333333334</v>
+        <v>46016.79166666666</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1737,10 +1741,10 @@
         <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="L20" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -1767,28 +1771,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DO_2_3</t>
+          <t>ORP_2_2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DO_2_3:step:20251209T16</t>
+          <t>ORP_2_2:regime:20260114T18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>46000.66666666666</v>
+        <v>46036.75</v>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>-0.1063214571657774</v>
+        <v>28.8906413334979</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46003.125</v>
+        <v>46038.45833333334</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1802,10 +1806,10 @@
         <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="L21" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -1832,12 +1836,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DO_2_3</t>
+          <t>ORP_2_2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DO_2_3:step:20251223T11</t>
+          <t>ORP_2_2:step:20260215T10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1846,14 +1850,14 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>46014.45833333334</v>
+        <v>46068.41666666666</v>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>0.2057443863673483</v>
+        <v>7.599198297838836</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46016.66666666666</v>
+        <v>46070.625</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1897,32 +1901,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DO_2_3</t>
+          <t>ORP_2_2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DO_2_3:step:20260117T11</t>
+          <t>ORP_2_2:regime:20260407T00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>46039.45833333334</v>
+        <v>46119</v>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>-0.5905287400200351</v>
+        <v>19.23473261139641</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46041.66666666666</v>
+        <v>46123.5</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>direct_recovery</t>
+          <t>adapted_recovery</t>
         </is>
       </c>
       <c r="I23" t="b">
@@ -1932,22 +1936,22 @@
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="L23" t="n">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q23" t="b">
         <v>0</v>
@@ -1956,1895 +1960,6 @@
         <v>0</v>
       </c>
       <c r="S23" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>DO_2_3</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>DO_2_3:step:20260219T08</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>46072.33333333334</v>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="n">
-        <v>0.6259566796065132</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>46074.54166666666</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>direct_recovery</t>
-        </is>
-      </c>
-      <c r="I24" t="b">
-        <v>0</v>
-      </c>
-      <c r="J24" t="b">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>53</v>
-      </c>
-      <c r="L24" t="n">
-        <v>53</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="b">
-        <v>0</v>
-      </c>
-      <c r="R24" t="b">
-        <v>0</v>
-      </c>
-      <c r="S24" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>DO_2_3</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>DO_2_3:step:20260323T13</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>46104.54166666666</v>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="n">
-        <v>0.2059832651611551</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>46106.75</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>direct_recovery</t>
-        </is>
-      </c>
-      <c r="I25" t="b">
-        <v>0</v>
-      </c>
-      <c r="J25" t="b">
-        <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>53</v>
-      </c>
-      <c r="L25" t="n">
-        <v>53</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="b">
-        <v>0</v>
-      </c>
-      <c r="R25" t="b">
-        <v>0</v>
-      </c>
-      <c r="S25" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>DO_2_3</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>DO_2_3:regime:pelt_20260323T04</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>46110</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>pelt_20260323T04</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>-0.482444813167461</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>46111.70833333334</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>direct_recovery</t>
-        </is>
-      </c>
-      <c r="I26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J26" t="b">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>41</v>
-      </c>
-      <c r="L26" t="n">
-        <v>41</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="b">
-        <v>0</v>
-      </c>
-      <c r="R26" t="b">
-        <v>0</v>
-      </c>
-      <c r="S26" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>DO_2_4</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>DO_2_4:step:20250922T00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>45922</v>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="n">
-        <v>-0.06918672521197838</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>45924.20833333334</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>direct_recovery</t>
-        </is>
-      </c>
-      <c r="I27" t="b">
-        <v>0</v>
-      </c>
-      <c r="J27" t="b">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>53</v>
-      </c>
-      <c r="L27" t="n">
-        <v>53</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="b">
-        <v>0</v>
-      </c>
-      <c r="R27" t="b">
-        <v>0</v>
-      </c>
-      <c r="S27" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>DO_2_4</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>DO_2_4:step:20251112T19</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>45973.79166666666</v>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="n">
-        <v>0.2017514910189401</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>45976</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>direct_recovery</t>
-        </is>
-      </c>
-      <c r="I28" t="b">
-        <v>0</v>
-      </c>
-      <c r="J28" t="b">
-        <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>53</v>
-      </c>
-      <c r="L28" t="n">
-        <v>53</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="b">
-        <v>0</v>
-      </c>
-      <c r="R28" t="b">
-        <v>0</v>
-      </c>
-      <c r="S28" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>DO_2_4</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>DO_2_4:step:20251122T14</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>45983.58333333334</v>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="n">
-        <v>-0.6015574562995701</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>45986.375</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>direct_recovery</t>
-        </is>
-      </c>
-      <c r="I29" t="b">
-        <v>0</v>
-      </c>
-      <c r="J29" t="b">
-        <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>67</v>
-      </c>
-      <c r="L29" t="n">
-        <v>67</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="b">
-        <v>1</v>
-      </c>
-      <c r="R29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>DO_2_4</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>DO_2_4:step:20251125T19</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>45986.79166666666</v>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="n">
-        <v>-0.1573813493024783</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>45989</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>direct_recovery</t>
-        </is>
-      </c>
-      <c r="I30" t="b">
-        <v>0</v>
-      </c>
-      <c r="J30" t="b">
-        <v>1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>53</v>
-      </c>
-      <c r="L30" t="n">
-        <v>53</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="b">
-        <v>0</v>
-      </c>
-      <c r="R30" t="b">
-        <v>0</v>
-      </c>
-      <c r="S30" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>DO_2_4</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>DO_2_4:step:20251207T15</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>45998.625</v>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="n">
-        <v>0.1257504797503055</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>46001.08333333334</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>direct_recovery</t>
-        </is>
-      </c>
-      <c r="I31" t="b">
-        <v>0</v>
-      </c>
-      <c r="J31" t="b">
-        <v>1</v>
-      </c>
-      <c r="K31" t="n">
-        <v>59</v>
-      </c>
-      <c r="L31" t="n">
-        <v>59</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="b">
-        <v>0</v>
-      </c>
-      <c r="R31" t="b">
-        <v>0</v>
-      </c>
-      <c r="S31" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>DO_2_4</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>DO_2_4:step:20251223T08</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>46014.33333333334</v>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="n">
-        <v>1.079469600632853</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>46016.54166666666</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>direct_recovery</t>
-        </is>
-      </c>
-      <c r="I32" t="b">
-        <v>0</v>
-      </c>
-      <c r="J32" t="b">
-        <v>1</v>
-      </c>
-      <c r="K32" t="n">
-        <v>53</v>
-      </c>
-      <c r="L32" t="n">
-        <v>53</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="b">
-        <v>0</v>
-      </c>
-      <c r="R32" t="b">
-        <v>0</v>
-      </c>
-      <c r="S32" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>DO_2_4</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>DO_2_4:step:20260107T10</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>46029.41666666666</v>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="n">
-        <v>0.01323905867822799</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>46031.625</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>direct_recovery</t>
-        </is>
-      </c>
-      <c r="I33" t="b">
-        <v>0</v>
-      </c>
-      <c r="J33" t="b">
-        <v>1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>53</v>
-      </c>
-      <c r="L33" t="n">
-        <v>53</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="b">
-        <v>0</v>
-      </c>
-      <c r="R33" t="b">
-        <v>0</v>
-      </c>
-      <c r="S33" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>ORP_1_2</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>ORP_1_2:regime:20251227T00</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>46018</v>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="n">
-        <v>-138.3913666949425</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>46028.54166666666</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>adapted_recovery</t>
-        </is>
-      </c>
-      <c r="I34" t="b">
-        <v>0</v>
-      </c>
-      <c r="J34" t="b">
-        <v>1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>253</v>
-      </c>
-      <c r="L34" t="n">
-        <v>253</v>
-      </c>
-      <c r="M34" t="n">
-        <v>7</v>
-      </c>
-      <c r="N34" t="n">
-        <v>2</v>
-      </c>
-      <c r="O34" t="n">
-        <v>9</v>
-      </c>
-      <c r="P34" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q34" t="b">
-        <v>0</v>
-      </c>
-      <c r="R34" t="b">
-        <v>0</v>
-      </c>
-      <c r="S34" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>ORP_1_2</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>ORP_1_2:step:20260115T22</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>46037.91666666666</v>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="n">
-        <v>-3.829514930719341</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>46040.125</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>direct_recovery</t>
-        </is>
-      </c>
-      <c r="I35" t="b">
-        <v>0</v>
-      </c>
-      <c r="J35" t="b">
-        <v>1</v>
-      </c>
-      <c r="K35" t="n">
-        <v>53</v>
-      </c>
-      <c r="L35" t="n">
-        <v>53</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="b">
-        <v>0</v>
-      </c>
-      <c r="R35" t="b">
-        <v>0</v>
-      </c>
-      <c r="S35" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>ORP_1_2</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>ORP_1_2:regime:20260217T00</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>46070</v>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="n">
-        <v>101.0772430934232</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>46087.66666666666</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>adapted_recovery</t>
-        </is>
-      </c>
-      <c r="I36" t="b">
-        <v>0</v>
-      </c>
-      <c r="J36" t="b">
-        <v>1</v>
-      </c>
-      <c r="K36" t="n">
-        <v>424</v>
-      </c>
-      <c r="L36" t="n">
-        <v>424</v>
-      </c>
-      <c r="M36" t="n">
-        <v>13</v>
-      </c>
-      <c r="N36" t="n">
-        <v>3</v>
-      </c>
-      <c r="O36" t="n">
-        <v>10</v>
-      </c>
-      <c r="P36" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q36" t="b">
-        <v>0</v>
-      </c>
-      <c r="R36" t="b">
-        <v>0</v>
-      </c>
-      <c r="S36" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>ORP_1_3</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>ORP_1_3:step:20250804T05</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="n">
-        <v>45873.20833333334</v>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="n">
-        <v>-256.7390325702373</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>45875.41666666666</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>direct_recovery</t>
-        </is>
-      </c>
-      <c r="I37" t="b">
-        <v>0</v>
-      </c>
-      <c r="J37" t="b">
-        <v>1</v>
-      </c>
-      <c r="K37" t="n">
-        <v>53</v>
-      </c>
-      <c r="L37" t="n">
-        <v>53</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R37" t="b">
-        <v>0</v>
-      </c>
-      <c r="S37" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>ORP_1_3</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>ORP_1_3:step:20250810T16</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>45879.66666666666</v>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="n">
-        <v>-11.2423278068691</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>45881.875</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>direct_recovery</t>
-        </is>
-      </c>
-      <c r="I38" t="b">
-        <v>0</v>
-      </c>
-      <c r="J38" t="b">
-        <v>1</v>
-      </c>
-      <c r="K38" t="n">
-        <v>53</v>
-      </c>
-      <c r="L38" t="n">
-        <v>53</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="b">
-        <v>0</v>
-      </c>
-      <c r="R38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S38" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>ORP_1_3</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>ORP_1_3:step:20250818T00</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="n">
-        <v>45887</v>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="n">
-        <v>11.84879610474837</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>45889.20833333334</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>direct_recovery</t>
-        </is>
-      </c>
-      <c r="I39" t="b">
-        <v>0</v>
-      </c>
-      <c r="J39" t="b">
-        <v>1</v>
-      </c>
-      <c r="K39" t="n">
-        <v>53</v>
-      </c>
-      <c r="L39" t="n">
-        <v>53</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="b">
-        <v>0</v>
-      </c>
-      <c r="R39" t="b">
-        <v>0</v>
-      </c>
-      <c r="S39" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>ORP_1_3</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>ORP_1_3:step:20250912T03</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>45912.125</v>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="n">
-        <v>-5.664233999419736</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>45914.33333333334</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>direct_recovery</t>
-        </is>
-      </c>
-      <c r="I40" t="b">
-        <v>0</v>
-      </c>
-      <c r="J40" t="b">
-        <v>1</v>
-      </c>
-      <c r="K40" t="n">
-        <v>53</v>
-      </c>
-      <c r="L40" t="n">
-        <v>53</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="b">
-        <v>0</v>
-      </c>
-      <c r="R40" t="b">
-        <v>0</v>
-      </c>
-      <c r="S40" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>ORP_1_3</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>ORP_1_3:step:20251008T08</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="n">
-        <v>45938.33333333334</v>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="n">
-        <v>-45.52594036613499</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>45941.29166666666</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>direct_recovery</t>
-        </is>
-      </c>
-      <c r="I41" t="b">
-        <v>0</v>
-      </c>
-      <c r="J41" t="b">
-        <v>1</v>
-      </c>
-      <c r="K41" t="n">
-        <v>71</v>
-      </c>
-      <c r="L41" t="n">
-        <v>71</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="b">
-        <v>0</v>
-      </c>
-      <c r="R41" t="b">
-        <v>0</v>
-      </c>
-      <c r="S41" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>ORP_1_3</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>ORP_1_3:step:20251014T08</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="n">
-        <v>45944.33333333334</v>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="n">
-        <v>-3.938976892889883</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>45950.875</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>adapted_recovery</t>
-        </is>
-      </c>
-      <c r="I42" t="b">
-        <v>0</v>
-      </c>
-      <c r="J42" t="b">
-        <v>1</v>
-      </c>
-      <c r="K42" t="n">
-        <v>157</v>
-      </c>
-      <c r="L42" t="n">
-        <v>157</v>
-      </c>
-      <c r="M42" t="n">
-        <v>2</v>
-      </c>
-      <c r="N42" t="n">
-        <v>2</v>
-      </c>
-      <c r="O42" t="n">
-        <v>9</v>
-      </c>
-      <c r="P42" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q42" t="b">
-        <v>1</v>
-      </c>
-      <c r="R42" t="b">
-        <v>1</v>
-      </c>
-      <c r="S42" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>ORP_1_3</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>ORP_1_3:step:20251021T13</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="n">
-        <v>45951.54166666666</v>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="n">
-        <v>188.7878666813279</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>45953.75</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>direct_recovery</t>
-        </is>
-      </c>
-      <c r="I43" t="b">
-        <v>0</v>
-      </c>
-      <c r="J43" t="b">
-        <v>1</v>
-      </c>
-      <c r="K43" t="n">
-        <v>53</v>
-      </c>
-      <c r="L43" t="n">
-        <v>53</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="b">
-        <v>0</v>
-      </c>
-      <c r="R43" t="b">
-        <v>0</v>
-      </c>
-      <c r="S43" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>ORP_1_3</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>ORP_1_3:step:20251123T11</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="n">
-        <v>45984.45833333334</v>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="n">
-        <v>54.87954550311956</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>45987.125</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>direct_recovery</t>
-        </is>
-      </c>
-      <c r="I44" t="b">
-        <v>0</v>
-      </c>
-      <c r="J44" t="b">
-        <v>1</v>
-      </c>
-      <c r="K44" t="n">
-        <v>64</v>
-      </c>
-      <c r="L44" t="n">
-        <v>64</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="b">
-        <v>0</v>
-      </c>
-      <c r="R44" t="b">
-        <v>0</v>
-      </c>
-      <c r="S44" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>ORP_1_3</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>ORP_1_3:step:20251204T08</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="n">
-        <v>45995.33333333334</v>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="n">
-        <v>86.42429231388056</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>45997.54166666666</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>direct_recovery</t>
-        </is>
-      </c>
-      <c r="I45" t="b">
-        <v>0</v>
-      </c>
-      <c r="J45" t="b">
-        <v>1</v>
-      </c>
-      <c r="K45" t="n">
-        <v>53</v>
-      </c>
-      <c r="L45" t="n">
-        <v>53</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="b">
-        <v>0</v>
-      </c>
-      <c r="R45" t="b">
-        <v>0</v>
-      </c>
-      <c r="S45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>ORP_1_3</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>ORP_1_3:step:20251211T17</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="n">
-        <v>46002.70833333334</v>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="n">
-        <v>-75.7388109247696</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>46004.91666666666</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>direct_recovery</t>
-        </is>
-      </c>
-      <c r="I46" t="b">
-        <v>0</v>
-      </c>
-      <c r="J46" t="b">
-        <v>1</v>
-      </c>
-      <c r="K46" t="n">
-        <v>53</v>
-      </c>
-      <c r="L46" t="n">
-        <v>53</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="b">
-        <v>0</v>
-      </c>
-      <c r="R46" t="b">
-        <v>0</v>
-      </c>
-      <c r="S46" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>ORP_1_3</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>ORP_1_3:step:20251223T11</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="n">
-        <v>46014.45833333334</v>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="n">
-        <v>41.54891625848991</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>46016.66666666666</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>direct_recovery</t>
-        </is>
-      </c>
-      <c r="I47" t="b">
-        <v>0</v>
-      </c>
-      <c r="J47" t="b">
-        <v>1</v>
-      </c>
-      <c r="K47" t="n">
-        <v>53</v>
-      </c>
-      <c r="L47" t="n">
-        <v>53</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="b">
-        <v>0</v>
-      </c>
-      <c r="R47" t="b">
-        <v>0</v>
-      </c>
-      <c r="S47" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>ORP_1_3</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>ORP_1_3:step:20260219T19</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="n">
-        <v>46072.79166666666</v>
-      </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="n">
-        <v>85.26952709458126</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>46075</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>direct_recovery</t>
-        </is>
-      </c>
-      <c r="I48" t="b">
-        <v>0</v>
-      </c>
-      <c r="J48" t="b">
-        <v>1</v>
-      </c>
-      <c r="K48" t="n">
-        <v>53</v>
-      </c>
-      <c r="L48" t="n">
-        <v>53</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="b">
-        <v>0</v>
-      </c>
-      <c r="R48" t="b">
-        <v>0</v>
-      </c>
-      <c r="S48" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>ORP_2_2</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>ORP_2_2:regime:20260114T18</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="n">
-        <v>46036.75</v>
-      </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="n">
-        <v>28.90134949475111</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>46038.45833333334</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>direct_recovery</t>
-        </is>
-      </c>
-      <c r="I49" t="b">
-        <v>0</v>
-      </c>
-      <c r="J49" t="b">
-        <v>1</v>
-      </c>
-      <c r="K49" t="n">
-        <v>41</v>
-      </c>
-      <c r="L49" t="n">
-        <v>41</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="b">
-        <v>0</v>
-      </c>
-      <c r="R49" t="b">
-        <v>0</v>
-      </c>
-      <c r="S49" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>ORP_2_2</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>ORP_2_2:step:20260215T08</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="n">
-        <v>46068.33333333334</v>
-      </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="n">
-        <v>6.539066213888471</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>46070.79166666666</v>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>direct_recovery</t>
-        </is>
-      </c>
-      <c r="I50" t="b">
-        <v>0</v>
-      </c>
-      <c r="J50" t="b">
-        <v>1</v>
-      </c>
-      <c r="K50" t="n">
-        <v>59</v>
-      </c>
-      <c r="L50" t="n">
-        <v>59</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="b">
-        <v>0</v>
-      </c>
-      <c r="R50" t="b">
-        <v>1</v>
-      </c>
-      <c r="S50" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>ORP_2_2</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>ORP_2_2:step:20260218T22</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="n">
-        <v>46071.91666666666</v>
-      </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="n">
-        <v>0.950264712180708</v>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>46074.125</v>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>direct_recovery</t>
-        </is>
-      </c>
-      <c r="I51" t="b">
-        <v>0</v>
-      </c>
-      <c r="J51" t="b">
-        <v>1</v>
-      </c>
-      <c r="K51" t="n">
-        <v>53</v>
-      </c>
-      <c r="L51" t="n">
-        <v>53</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="b">
-        <v>0</v>
-      </c>
-      <c r="R51" t="b">
-        <v>0</v>
-      </c>
-      <c r="S51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>ORP_2_2</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>ORP_2_2:regime:20260407T00</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="n">
-        <v>46119</v>
-      </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="n">
-        <v>19.2347326113964</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>46123.5</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>adapted_recovery</t>
-        </is>
-      </c>
-      <c r="I52" t="b">
-        <v>0</v>
-      </c>
-      <c r="J52" t="b">
-        <v>1</v>
-      </c>
-      <c r="K52" t="n">
-        <v>108</v>
-      </c>
-      <c r="L52" t="n">
-        <v>108</v>
-      </c>
-      <c r="M52" t="n">
-        <v>1</v>
-      </c>
-      <c r="N52" t="n">
-        <v>1</v>
-      </c>
-      <c r="O52" t="n">
-        <v>10</v>
-      </c>
-      <c r="P52" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q52" t="b">
-        <v>0</v>
-      </c>
-      <c r="R52" t="b">
-        <v>0</v>
-      </c>
-      <c r="S52" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3986,52 +2101,52 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5649937852319399</v>
+        <v>0.3755282641185388</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9801096286728695</v>
+        <v>0.9637768390302125</v>
       </c>
       <c r="K2" t="n">
-        <v>53</v>
+        <v>53.5</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>9</v>
@@ -4040,7 +2155,7 @@
         <v>0.003910068426197458</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003421309872922776</v>
+        <v>0.001466275659824047</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -4059,28 +2174,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5655085052479191</v>
+        <v>0.2065432914738929</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -4126,28 +2241,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7411599827511859</v>
+        <v>0.5100999795960008</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -4159,28 +2274,28 @@
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.05882352941176471</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S4" t="n">
-        <v>0.005050505050505051</v>
+        <v>0.006679700228087325</v>
       </c>
       <c r="T4" t="n">
-        <v>0.007168458781362007</v>
+        <v>0.01971326164874552</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -4199,28 +2314,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6456611570247934</v>
+        <v>0.3423719528896192</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -4250,13 +2365,13 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1428571428571428</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1428571428571428</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1428571428571428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4293,34 +2408,34 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>0.25</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01221896383186706</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01955034213098729</v>
+        <v>0.01319648093841642</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -4339,28 +2454,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7574992425007574</v>
+        <v>0.5100999795960008</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -4387,22 +2502,22 @@
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S7" t="n">
-        <v>0.005702183121537961</v>
+        <v>0.004398826979472141</v>
       </c>
       <c r="T7" t="n">
-        <v>0.002932551319648094</v>
+        <v>0.003095470837406321</v>
       </c>
       <c r="U7" t="n">
-        <v>0.08333333333333333</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.08333333333333333</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.08333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4412,34 +2527,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
         <v>3</v>
       </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>4</v>
-      </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5100999795960008</v>
+        <v>0.4384939195509823</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="L8" t="n">
         <v>1</v>
@@ -4472,10 +2587,10 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4485,70 +2600,70 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="F9" t="n">
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9803921568627451</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8969519232441061</v>
+        <v>0.7820151050048196</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9965303967465577</v>
+        <v>0.9919307806988522</v>
       </c>
       <c r="K9" t="n">
         <v>53</v>
       </c>
       <c r="L9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M9" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="N9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O9" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.1538461538461539</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S9" t="n">
-        <v>0.002199413489736071</v>
+        <v>0.002071405297211749</v>
       </c>
       <c r="T9" t="n">
-        <v>0.002478704091607318</v>
+        <v>0.00279290601871247</v>
       </c>
       <c r="U9" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4562,7 +2677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4602,7 +2717,7 @@
         <v>41</v>
       </c>
       <c r="B2" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="C2" t="n">
         <v>2</v>
@@ -4611,10 +2726,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9607843137254902</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03921568627450978</v>
+        <v>0.09090909090909094</v>
       </c>
     </row>
     <row r="3">
@@ -4622,27 +2737,27 @@
         <v>53</v>
       </c>
       <c r="B3" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3529411764705882</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6470588235294118</v>
+        <v>0.6363636363636364</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
@@ -4651,58 +2766,58 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.6818181818181819</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3137254901960784</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6862745098039216</v>
+        <v>0.6818181818181819</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2549019607843137</v>
+        <v>0.2651515151515151</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7450980392156863</v>
+        <v>0.7348484848484849</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>63</v>
+        <v>108</v>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -4711,38 +2826,38 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.2121212121212121</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7647058823529411</v>
+        <v>0.7878787878787878</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>64</v>
+        <v>145</v>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.196078431372549</v>
+        <v>0.1590909090909091</v>
       </c>
       <c r="F8" t="n">
-        <v>0.803921568627451</v>
+        <v>0.8409090909090909</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>67</v>
+        <v>272</v>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -4751,18 +2866,18 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1764705882352941</v>
+        <v>0.1060606060606061</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.8939393939393939</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>70</v>
+        <v>487</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
@@ -4771,18 +2886,18 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1568627450980392</v>
+        <v>0.05303030303030304</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8431372549019608</v>
+        <v>0.946969696969697</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>71</v>
+        <v>625</v>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
@@ -4791,149 +2906,9 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1372549019607843</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8627450980392157</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>97</v>
-      </c>
-      <c r="B12" t="n">
-        <v>7</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.1176470588235294</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.8823529411764706</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>108</v>
-      </c>
-      <c r="B13" t="n">
-        <v>6</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.09803921568627452</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.9019607843137255</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>139</v>
-      </c>
-      <c r="B14" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.09803921568627452</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.9019607843137255</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>157</v>
-      </c>
-      <c r="B15" t="n">
-        <v>4</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.0735294117647059</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.9264705882352942</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>253</v>
-      </c>
-      <c r="B16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.04901960784313727</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.9509803921568627</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>262</v>
-      </c>
-      <c r="B17" t="n">
-        <v>2</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.02450980392156863</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.9754901960784313</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>424</v>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4980,10 +2955,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="B2" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/data/D1_recovery_event_audit.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/data/D1_recovery_event_audit.xlsx
@@ -1337,7 +1337,7 @@
         <v>-138.3912907061892</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46029.33333333334</v>
+        <v>46029.29166666666</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1351,13 +1351,13 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L14" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="M14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
@@ -1487,7 +1487,7 @@
         <v>487</v>
       </c>
       <c r="M16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N16" t="n">
         <v>3</v>
@@ -2408,7 +2408,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -2435,7 +2435,7 @@
         <v>0.0101010101010101</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01319648093841642</v>
+        <v>0.01417399804496579</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
         <v>0.002071405297211749</v>
       </c>
       <c r="T9" t="n">
-        <v>0.00279290601871247</v>
+        <v>0.002862728669180282</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -2854,7 +2854,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B9" t="n">
         <v>3</v>
